--- a/data/tags/אלבומים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-03-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הילה רוח – שחור זוהר</v>
+        <v>אייל גולן - 30 חלק ב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%a9%d7%97%d7%95%d7%a8-%d7%96%d7%95%d7%94%d7%a8/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24462&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-25</v>
+        <v>2026-03-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"שחור זוהר" של הילה רוח הוא יצירה בת 15 שירים שמנסה להלך על קו עדין בין פופ נגיש לבין אמירה כמעט אוונגרדית.  זה לא אלבום שמבקש לרצות אלא  להטרי, לעורר, ולפעמים גם לבלבל. הסינגלים "טבע" ו־"זאת השנה" מתפקדים כשער כניסה</v>
+        <v>16:05</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הילה רוח – שחור זוהר</v>
+        <v>אייל גולן - 30 חלק ב</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אגם בוחבוט - פריפריה אקספרס</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24460&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>15:58</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אגם בוחבוט - פריפריה אקספרס</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24458&amp;forum=music&amp;viewmode=all</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-27</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>15:52</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>אלבומים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/2026-03-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-03-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - 30 חלק ב</v>
+        <v>רובין Sexistential</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24462&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%91%d7%99%d7%9f-sexistential/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16:05</v>
+        <v>בקריירה שנמשכת כבר שני עשורים, רובין (Robyn), הזמרת השוודית, יצרה כמה מהלהיטים הבולטים בפופ – ובראשם “Dancing On My Own”, המנון נצחי ואיקוני על מציאת הדרך האישית מתוך שברון לב. אך באלבומה התשיעי “Sexistential”, אנו פוגשים אותה חסרת עוגן ותוהה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - 30 חלק ב</v>
+        <v>רובין Sexistential</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אגם בוחבוט - פריפריה אקספרס</v>
+        <v>עידן רייכל - הד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24460&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24457&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15:58</v>
+        <v>01:19</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,27 +507,27 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אגם בוחבוט - פריפריה אקספרס</v>
+        <v>עידן רייכל - הד</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
+        <v>אייל גולן - 30 - חלק א</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-27</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24458&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24461&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-03-27</v>
+        <v>2026-03-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>15:52</v>
+        <v>16:00</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,7 +545,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עדן בן זקן - היכל מנורה 2025 LIVE</v>
+        <v>אייל גולן - 30 - חלק א</v>
       </c>
     </row>
   </sheetData>
